--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_29-05-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_29-05-2026.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£15.52</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>£34.42</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Max retries exceeded with url: /90mm-recticel-gp-insulation-board-2400x1200mm-9-p.asp (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='onlineinsulation-sales.com', port=443) at 0x29c0d751c90&gt;, 'Connection to onlineinsulation-sales.com timed out. (connect timeout=None)'))</t>
+          <t>£41.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£300</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625901440</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/115mm-recticel-eurowall-full-fill-cavity-wall-insulation-1200mm-x-460mm</t>
+          <t>£703.35</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/recticel-eurowall-full-fill-cavity?variant=42960350642229</t>
+          <t>£350</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_29-05-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_29-05-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3207CE-0D81-42F4-B153-67FCB63AC4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5365ABD9-8FB8-4C6A-8C4E-FAA68E3DD1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34395" yWindow="480" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31200" yWindow="2235" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -766,9 +766,6 @@
     <t>£600.0</t>
   </si>
   <si>
-    <t>£141.19</t>
-  </si>
-  <si>
     <t>£836.5</t>
   </si>
   <si>
@@ -793,9 +790,6 @@
     <t>£670.45</t>
   </si>
   <si>
-    <t>£143.21</t>
-  </si>
-  <si>
     <t>£729.35</t>
   </si>
   <si>
@@ -830,6 +824,12 @@
   </si>
   <si>
     <t>£276.59</t>
+  </si>
+  <si>
+    <t>£705.95</t>
+  </si>
+  <si>
+    <t>£716.05</t>
   </si>
 </sst>
 </file>
@@ -2099,7 +2099,7 @@
         <v>214</v>
       </c>
       <c r="C17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D17" t="s">
         <v>31</v>
@@ -2459,36 +2459,36 @@
         <v>27</v>
       </c>
       <c r="K23" t="s">
+        <v>268</v>
+      </c>
+      <c r="L23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" t="s">
         <v>248</v>
       </c>
-      <c r="L23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>249</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>250</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>27</v>
+      </c>
+      <c r="R23" t="s">
         <v>251</v>
-      </c>
-      <c r="P23" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>27</v>
-      </c>
-      <c r="R23" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>252</v>
+      </c>
+      <c r="B24" t="s">
         <v>253</v>
-      </c>
-      <c r="B24" t="s">
-        <v>254</v>
       </c>
       <c r="C24" t="s">
         <v>245</v>
@@ -2503,11 +2503,11 @@
         <v>27</v>
       </c>
       <c r="G24" t="s">
+        <v>254</v>
+      </c>
+      <c r="H24" t="s">
         <v>255</v>
       </c>
-      <c r="H24" t="s">
-        <v>256</v>
-      </c>
       <c r="I24" t="s">
         <v>27</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>27</v>
       </c>
       <c r="K24" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="L24" t="s">
         <v>27</v>
@@ -2524,10 +2524,10 @@
         <v>31</v>
       </c>
       <c r="N24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O24" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P24" t="s">
         <v>27</v>
@@ -2536,42 +2536,42 @@
         <v>27</v>
       </c>
       <c r="R24" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>258</v>
+      </c>
+      <c r="B25" t="s">
+        <v>259</v>
+      </c>
+      <c r="C25" t="s">
         <v>260</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
+        <v>260</v>
+      </c>
+      <c r="E25" t="s">
+        <v>260</v>
+      </c>
+      <c r="F25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" t="s">
         <v>261</v>
       </c>
-      <c r="C25" t="s">
+      <c r="H25" t="s">
         <v>262</v>
       </c>
-      <c r="D25" t="s">
-        <v>262</v>
-      </c>
-      <c r="E25" t="s">
-        <v>262</v>
-      </c>
-      <c r="F25" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" t="s">
         <v>263</v>
-      </c>
-      <c r="H25" t="s">
-        <v>264</v>
-      </c>
-      <c r="I25" t="s">
-        <v>27</v>
-      </c>
-      <c r="J25" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" t="s">
-        <v>265</v>
       </c>
       <c r="L25" t="s">
         <v>27</v>
@@ -2580,19 +2580,19 @@
         <v>31</v>
       </c>
       <c r="N25" t="s">
+        <v>264</v>
+      </c>
+      <c r="O25" t="s">
+        <v>265</v>
+      </c>
+      <c r="P25" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>27</v>
+      </c>
+      <c r="R25" t="s">
         <v>266</v>
-      </c>
-      <c r="O25" t="s">
-        <v>267</v>
-      </c>
-      <c r="P25" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>27</v>
-      </c>
-      <c r="R25" t="s">
-        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_29-05-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_29-05-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5365ABD9-8FB8-4C6A-8C4E-FAA68E3DD1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDEFFFF-27D2-466D-B89C-F5834A7363A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31200" yWindow="2235" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1377,7 +1377,7 @@
         <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
         <v>50</v>
